--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F70AAA2-95BC-4A2F-B0BC-83132FC5A541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0958A2CB-7222-4472-B7C9-3A03BDB05724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>nama</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>doni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alamat </t>
+  </si>
+  <si>
+    <t>pebayuran</t>
   </si>
 </sst>
 </file>
@@ -357,10 +363,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -370,8 +376,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -380,6 +389,9 @@
       </c>
       <c r="C2" t="s">
         <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
